--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488098_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488098_PROCESSED_CHRONO.xlsx
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.6458</v>
+        <v>-0.7519</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.2848</v>
+        <v>-1.2224</v>
       </c>
       <c r="F3" t="n">
-        <v>0.639</v>
+        <v>0.4705</v>
       </c>
       <c r="G3" t="n">
         <v>-0.0416</v>
@@ -688,13 +688,13 @@
         <v>0.7929</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.406</v>
+        <v>-0.5121</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3744</v>
+        <v>-0.312</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0316</v>
+        <v>-0.2001</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. OULAI</t>
+          <t>A. MORENO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.6482</v>
+        <v>-0.8758</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9991</v>
+        <v>3.0655</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.6473</v>
+        <v>-3.9414</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.751</v>
+        <v>-0.7893</v>
       </c>
       <c r="H4" t="n">
-        <v>1.5016</v>
+        <v>-0.9119</v>
       </c>
       <c r="I4" t="n">
-        <v>-3.2526</v>
+        <v>0.1226</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4948</v>
+        <v>5.2131</v>
       </c>
       <c r="K4" t="n">
-        <v>3.9692</v>
+        <v>2.3008</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.4744</v>
+        <v>2.9122</v>
       </c>
       <c r="M4" t="n">
-        <v>-5.2459</v>
+        <v>-6.0024</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.4676</v>
+        <v>-3.2127</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.7782</v>
+        <v>-2.7896</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1893</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9822</v>
+        <v>-3.9645</v>
       </c>
       <c r="R4" t="n">
         <v>3.1716</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2827</v>
+        <v>-1.7078</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2903</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.573</v>
+        <v>-1.1106</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1962</v>
+        <v>2.4142</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1962</v>
+        <v>2.4142</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. CARRAL ESCUDERO</t>
+          <t>B. GIMENEZ SALAZAR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.2666</v>
+        <v>-0.9695</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3524</v>
+        <v>3.9222</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.619</v>
+        <v>-4.8916</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.0636</v>
+        <v>0.8377</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.655</v>
+        <v>1.4616</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.4086</v>
+        <v>-0.6239</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2184</v>
+        <v>5.4818</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6059</v>
+        <v>3.9952</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.8243</v>
+        <v>1.4866</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.8452</v>
+        <v>-4.6441</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.2609</v>
+        <v>-2.5336</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.5843</v>
+        <v>-2.1105</v>
       </c>
       <c r="P5" t="n">
-        <v>1.9822</v>
+        <v>1.1893</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9822</v>
+        <v>3.1716</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.3924</v>
+        <v>-2.1263</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5064</v>
+        <v>-0.7844</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8859</v>
+        <v>-1.3419</v>
       </c>
       <c r="V5" t="n">
+        <v>-0.8701</v>
+      </c>
+      <c r="W5" t="n">
         <v>1.2071</v>
       </c>
-      <c r="W5" t="n">
-        <v>2.0772</v>
-      </c>
       <c r="X5" t="n">
-        <v>-0.8701</v>
+        <v>-2.0772</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. MORENO</t>
+          <t>G. CARRAL ESCUDERO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.8198</v>
+        <v>-1.3903</v>
       </c>
       <c r="E6" t="n">
-        <v>2.2901</v>
+        <v>1.3129</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.1098</v>
+        <v>-2.7033</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7893</v>
+        <v>-3.0636</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9119</v>
+        <v>-0.655</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1226</v>
+        <v>-2.4086</v>
       </c>
       <c r="J6" t="n">
-        <v>5.2131</v>
+        <v>-0.2184</v>
       </c>
       <c r="K6" t="n">
-        <v>2.3008</v>
+        <v>0.6059</v>
       </c>
       <c r="L6" t="n">
-        <v>2.9122</v>
+        <v>-0.8243</v>
       </c>
       <c r="M6" t="n">
-        <v>-6.0024</v>
+        <v>-2.8452</v>
       </c>
       <c r="N6" t="n">
-        <v>-3.2127</v>
+        <v>-1.2609</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.7896</v>
+        <v>-1.5843</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.7929</v>
+        <v>1.9822</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.9645</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>3.1716</v>
+        <v>1.9822</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.6518</v>
+        <v>-1.5161</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.3727</v>
+        <v>-0.5459000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.279</v>
+        <v>-0.9702</v>
       </c>
       <c r="V6" t="n">
-        <v>2.4142</v>
+        <v>1.2071</v>
       </c>
       <c r="W6" t="n">
-        <v>2.4142</v>
+        <v>2.0772</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.8701</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. GIMENEZ SALAZAR</t>
+          <t>K. OULAI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,40 +955,40 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.9758</v>
+        <v>-1.8999</v>
       </c>
       <c r="E7" t="n">
-        <v>3.0843</v>
+        <v>1.3089</v>
       </c>
       <c r="F7" t="n">
-        <v>-5.0601</v>
+        <v>-3.2088</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8377</v>
+        <v>-1.751</v>
       </c>
       <c r="H7" t="n">
-        <v>1.4616</v>
+        <v>1.5016</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6239</v>
+        <v>-3.2526</v>
       </c>
       <c r="J7" t="n">
-        <v>5.4818</v>
+        <v>3.4948</v>
       </c>
       <c r="K7" t="n">
-        <v>3.9952</v>
+        <v>3.9692</v>
       </c>
       <c r="L7" t="n">
-        <v>1.4866</v>
+        <v>-0.4744</v>
       </c>
       <c r="M7" t="n">
-        <v>-4.6441</v>
+        <v>-5.2459</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.5336</v>
+        <v>-2.4676</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.1105</v>
+        <v>-2.7782</v>
       </c>
       <c r="P7" t="n">
         <v>1.1893</v>
@@ -1000,22 +1000,22 @@
         <v>3.1716</v>
       </c>
       <c r="S7" t="n">
-        <v>-3.1327</v>
+        <v>-1.5344</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.6223</v>
+        <v>-0.3999</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.5104</v>
+        <v>-1.1345</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.8701</v>
+        <v>0.1962</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2071</v>
+        <v>0.1962</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.0772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.2996</v>
+        <v>-1.9107</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.1874</v>
+        <v>-2.0231</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1122</v>
+        <v>0.1125</v>
       </c>
       <c r="G8" t="n">
         <v>-0.6814</v>
@@ -1078,13 +1078,13 @@
         <v>0.5947</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9550999999999999</v>
+        <v>-0.5662</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5616</v>
+        <v>-0.3973</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3936</v>
+        <v>-0.1689</v>
       </c>
       <c r="V8" t="n">
         <v>-0.2666</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.0742</v>
+        <v>-3.753</v>
       </c>
       <c r="E9" t="n">
-        <v>1.3941</v>
+        <v>0.7433999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.4683</v>
+        <v>-4.4963</v>
       </c>
       <c r="G9" t="n">
         <v>-3.2371</v>
@@ -1156,13 +1156,13 @@
         <v>2.5769</v>
       </c>
       <c r="S9" t="n">
-        <v>0.07679999999999999</v>
+        <v>-0.602</v>
       </c>
       <c r="T9" t="n">
-        <v>0.727</v>
+        <v>0.0764</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6503</v>
+        <v>-0.6784</v>
       </c>
       <c r="V9" t="n">
         <v>1.4737</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.6348</v>
+        <v>-7.1897</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6825</v>
+        <v>-1.5182</v>
       </c>
       <c r="F10" t="n">
-        <v>-5.9523</v>
+        <v>-5.6715</v>
       </c>
       <c r="G10" t="n">
         <v>-5.6479</v>
@@ -1234,13 +1234,13 @@
         <v>2.9733</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.1584</v>
+        <v>-1.7133</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5064</v>
+        <v>-0.3422</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.652</v>
+        <v>-1.3712</v>
       </c>
       <c r="V10" t="n">
         <v>-1.8107</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-18.6455</v>
+        <v>-18.0215</v>
       </c>
       <c r="E11" t="n">
-        <v>5.288099999999999</v>
+        <v>5.912000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-23.9336</v>
+        <v>-23.9335</v>
       </c>
       <c r="G11" t="n">
         <v>-14.0514</v>
@@ -1291,7 +1291,7 @@
         <v>13.0174</v>
       </c>
       <c r="L11" t="n">
-        <v>2.488299999999999</v>
+        <v>2.4883</v>
       </c>
       <c r="M11" t="n">
         <v>-29.5574</v>
@@ -1312,10 +1312,10 @@
         <v>18.8312</v>
       </c>
       <c r="S11" t="n">
-        <v>-10.9023</v>
+        <v>-10.2782</v>
       </c>
       <c r="T11" t="n">
-        <v>-3.9265</v>
+        <v>-3.3026</v>
       </c>
       <c r="U11" t="n">
         <v>-6.9758</v>
@@ -1327,7 +1327,7 @@
         <v>8.5755</v>
       </c>
       <c r="X11" t="n">
-        <v>-6.2317</v>
+        <v>-6.231699999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>9.760300000000001</v>
+        <v>8.3028</v>
       </c>
       <c r="E12" t="n">
-        <v>10.9845</v>
+        <v>9.863899999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.2242</v>
+        <v>-1.5611</v>
       </c>
       <c r="G12" t="n">
         <v>5.152</v>
@@ -1390,13 +1390,13 @@
         <v>1.784</v>
       </c>
       <c r="S12" t="n">
-        <v>3.4278</v>
+        <v>1.9703</v>
       </c>
       <c r="T12" t="n">
-        <v>2.8451</v>
+        <v>1.7245</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5827</v>
+        <v>0.2458</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6036</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.4812</v>
+        <v>7.528</v>
       </c>
       <c r="E13" t="n">
-        <v>6.7049</v>
+        <v>7.7236</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2237</v>
+        <v>-0.1956</v>
       </c>
       <c r="G13" t="n">
         <v>3.8853</v>
@@ -1468,13 +1468,13 @@
         <v>2.3787</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1728</v>
+        <v>1.2196</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.132</v>
+        <v>0.8867</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3049</v>
+        <v>0.3329</v>
       </c>
       <c r="V13" t="n">
         <v>3.0178</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R. SANCHES CARDOSO MENDES</t>
+          <t>M. HETOR MENSAH</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.7141</v>
+        <v>6.5169</v>
       </c>
       <c r="E14" t="n">
-        <v>4.8835</v>
+        <v>5.3855</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8306</v>
+        <v>1.1315</v>
       </c>
       <c r="G14" t="n">
-        <v>3.7151</v>
+        <v>6.7165</v>
       </c>
       <c r="H14" t="n">
-        <v>3.3573</v>
+        <v>0.9444</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3577</v>
+        <v>5.7721</v>
       </c>
       <c r="J14" t="n">
-        <v>3.8334</v>
+        <v>7.6869</v>
       </c>
       <c r="K14" t="n">
-        <v>3.753</v>
+        <v>1.9376</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0804</v>
+        <v>5.7493</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1184</v>
+        <v>-0.9704</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3957</v>
+        <v>-0.9932</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2774</v>
+        <v>0.0228</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7929</v>
+        <v>-1.1893</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-3.1716</v>
       </c>
       <c r="R14" t="n">
-        <v>0.7929</v>
+        <v>1.9822</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2062</v>
+        <v>1.2563</v>
       </c>
       <c r="T14" t="n">
-        <v>0.18</v>
+        <v>0.8701</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0262</v>
+        <v>0.3862</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
       <c r="W14" t="n">
-        <v>0.8701</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.8701</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. HETOR MENSAH</t>
+          <t>R. SANCHES CARDOSO MENDES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.6177</v>
+        <v>5.0154</v>
       </c>
       <c r="E15" t="n">
-        <v>4.5705</v>
+        <v>4.5779</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0472</v>
+        <v>0.4375</v>
       </c>
       <c r="G15" t="n">
-        <v>6.7165</v>
+        <v>3.7151</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9444</v>
+        <v>3.3573</v>
       </c>
       <c r="I15" t="n">
-        <v>5.7721</v>
+        <v>0.3577</v>
       </c>
       <c r="J15" t="n">
-        <v>7.6869</v>
+        <v>3.8334</v>
       </c>
       <c r="K15" t="n">
-        <v>1.9376</v>
+        <v>3.753</v>
       </c>
       <c r="L15" t="n">
-        <v>5.7493</v>
+        <v>0.0804</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.9704</v>
+        <v>-0.1184</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9932</v>
+        <v>-0.3957</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0228</v>
+        <v>0.2774</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.1893</v>
+        <v>0.7929</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.1716</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9822</v>
+        <v>0.7929</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3571</v>
+        <v>0.5075</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0552</v>
+        <v>-0.1257</v>
       </c>
       <c r="U15" t="n">
-        <v>0.302</v>
+        <v>0.6331</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.8701</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2666</v>
+        <v>-0.8701</v>
       </c>
     </row>
     <row r="16">
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. HIDALGO SALAZAR</t>
+          <t>A. DIAZ ROLLANO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8247</v>
+        <v>1.0745</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3008</v>
+        <v>2.4757</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5239</v>
+        <v>-1.4012</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4331</v>
+        <v>0.2491</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4331</v>
+        <v>-0.7707000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1.0197</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3632</v>
+        <v>3.3153</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3632</v>
+        <v>1.379</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.9363</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0699</v>
+        <v>-3.0662</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0699</v>
+        <v>-2.1497</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>-0.9166</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1982</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.1893</v>
       </c>
       <c r="R17" t="n">
-        <v>0.1982</v>
+        <v>1.1893</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1934</v>
+        <v>1.092</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0624</v>
+        <v>0.3497</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2558</v>
+        <v>0.7423</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. DIAZ ROLLANO</t>
+          <t>R. HIDALGO SALAZAR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7265</v>
+        <v>0.7405</v>
       </c>
       <c r="E18" t="n">
-        <v>1.7626</v>
+        <v>0.3008</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0361</v>
+        <v>0.4397</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2491</v>
+        <v>0.4331</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.7707000000000001</v>
+        <v>0.4331</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0197</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>3.3153</v>
+        <v>0.3632</v>
       </c>
       <c r="K18" t="n">
-        <v>1.379</v>
+        <v>0.3632</v>
       </c>
       <c r="L18" t="n">
-        <v>1.9363</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.0662</v>
+        <v>0.0699</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.1497</v>
+        <v>0.0699</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9166</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.1982</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1893</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1893</v>
+        <v>0.1982</v>
       </c>
       <c r="S18" t="n">
-        <v>0.744</v>
+        <v>0.1092</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3634</v>
+        <v>-0.0624</v>
       </c>
       <c r="U18" t="n">
-        <v>1.1073</v>
+        <v>0.1716</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. REID</t>
+          <t>A. GAVIRA LLERGO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1376</v>
+        <v>-0.3193</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5496</v>
+        <v>-0.681</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6872</v>
+        <v>0.3617</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.9655</v>
+        <v>-0.5487</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.7343</v>
+        <v>-0.5487</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2312</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.66</v>
+        <v>-0.6186</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5304</v>
+        <v>-0.6186</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.1296</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.3055</v>
+        <v>0.0699</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.2038</v>
+        <v>0.0699</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1016</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.1982</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.1805</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1805</v>
+        <v>0.1982</v>
       </c>
       <c r="S19" t="n">
-        <v>1.9577</v>
+        <v>0.0312</v>
       </c>
       <c r="T19" t="n">
-        <v>1.9164</v>
+        <v>-0.0624</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0413</v>
+        <v>0.0936</v>
       </c>
       <c r="V19" t="n">
-        <v>0.8701</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.4737</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. GAVIRA LLERGO</t>
+          <t>R. REID</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3755</v>
+        <v>-0.3838</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.681</v>
+        <v>-0.0616</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3055</v>
+        <v>-0.3222</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.5487</v>
+        <v>-2.9655</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5487</v>
+        <v>-2.7343</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>-0.2312</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6186</v>
+        <v>-0.66</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6186</v>
+        <v>-0.5304</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-0.1296</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0699</v>
+        <v>-2.3055</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0699</v>
+        <v>-2.2038</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>-0.1016</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1982</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.1805</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1982</v>
+        <v>2.1805</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.025</v>
+        <v>1.7115</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0624</v>
+        <v>1.3052</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0374</v>
+        <v>0.4064</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.8701</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.4737</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9034</v>
+        <v>-0.8473000000000001</v>
       </c>
       <c r="E21" t="n">
         <v>-0.0019</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9016</v>
+        <v>-0.8454</v>
       </c>
       <c r="G21" t="n">
         <v>0.1304</v>
@@ -2092,13 +2092,13 @@
         <v>0.1982</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.025</v>
+        <v>0.0312</v>
       </c>
       <c r="T21" t="n">
         <v>-0.0624</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0374</v>
+        <v>0.0936</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2071</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9989</v>
+        <v>-3.3574</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.1024</v>
+        <v>-3.7136</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1035</v>
+        <v>0.3562</v>
       </c>
       <c r="G22" t="n">
         <v>-2.9662</v>
@@ -2170,13 +2170,13 @@
         <v>2.5769</v>
       </c>
       <c r="S22" t="n">
-        <v>2.7602</v>
+        <v>2.4017</v>
       </c>
       <c r="T22" t="n">
-        <v>2.0412</v>
+        <v>1.43</v>
       </c>
       <c r="U22" t="n">
-        <v>0.719</v>
+        <v>0.9717</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2071</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.177</v>
+        <v>-7.7382</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.151</v>
+        <v>-4.0491</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.026</v>
+        <v>-3.6891</v>
       </c>
       <c r="G23" t="n">
         <v>-1.8629</v>
@@ -2248,13 +2248,13 @@
         <v>1.3876</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1329</v>
+        <v>0.5717</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6205000000000001</v>
+        <v>0.7224</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4876</v>
+        <v>-0.1506</v>
       </c>
       <c r="V23" t="n">
         <v>-2.6808</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>18.64540000000001</v>
+        <v>18.6454</v>
       </c>
       <c r="E24" t="n">
-        <v>23.9334</v>
+        <v>23.9335</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.2881</v>
+        <v>-5.287999999999999</v>
       </c>
       <c r="G24" t="n">
         <v>14.0515</v>
@@ -2299,7 +2299,7 @@
         <v>12.7323</v>
       </c>
       <c r="J24" t="n">
-        <v>29.5573</v>
+        <v>29.55730000000001</v>
       </c>
       <c r="K24" t="n">
         <v>14.3363</v>
@@ -2326,13 +2326,13 @@
         <v>14.8667</v>
       </c>
       <c r="S24" t="n">
-        <v>10.9021</v>
+        <v>10.9022</v>
       </c>
       <c r="T24" t="n">
-        <v>6.9758</v>
+        <v>6.9757</v>
       </c>
       <c r="U24" t="n">
-        <v>3.9264</v>
+        <v>3.9266</v>
       </c>
       <c r="V24" t="n">
         <v>-2.343900000000001</v>
